--- a/data/synthetic/rendered/oem_b.xlsx
+++ b/data/synthetic/rendered/oem_b.xlsx
@@ -847,7 +847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,6 +878,21 @@
           <t>Parameter octets</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Allowed modes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Access tier</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -900,6 +915,21 @@
           <t>{'1': 2, '2': 0}</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -922,6 +952,21 @@
           <t>{'1': 2, '2': 0}</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -944,10 +989,25 @@
           <t>{'1': 2, '2': 0}</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -959,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,6 +1050,16 @@
           <t>Security gate</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Subfunctions</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SPR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1003,6 +1073,19 @@
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1016,6 +1099,19 @@
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[{'value': 1, 'name': 'hard'}]</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1029,6 +1125,19 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1042,6 +1151,19 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1055,6 +1177,19 @@
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1072,8 +1207,18 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>2</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1088,10 +1233,23 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1193,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,14 +1364,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>The six operating conditions are ignition_on, speed_zero, doors_closed, battery_ok, vehicle_stopped, and service_brake.</t>
+          <t>DID 0x2000 may be written only when ignition_on is true.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Each condition must be true for its matching data identifier write.</t>
+          <t>Writing DID 0x2000 requires ignition_on to be true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DID 0x2000 must not be written while ignition_on is false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DID 0x2001 may be written only when speed_zero is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Writing DID 0x2001 requires speed_zero to be true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DID 0x2001 must not be written while speed_zero is false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DID 0x2002 may be written only when doors_closed is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Writing DID 0x2002 requires doors_closed to be true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DID 0x2002 must not be written while doors_closed is false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DID 0x2003 may be written only when battery_ok is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Writing DID 0x2003 requires battery_ok to be true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DID 0x2003 must not be written while battery_ok is false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DID 0x2004 may be written only when vehicle_stopped is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Writing DID 0x2004 requires vehicle_stopped to be true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DID 0x2004 must not be written while vehicle_stopped is false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DID 0x2005 may be written only when service_brake is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Writing DID 0x2005 requires service_brake to be true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DID 0x2005 must not be written while service_brake is false.</t>
         </is>
       </c>
     </row>

--- a/data/synthetic/rendered/oem_b.xlsx
+++ b/data/synthetic/rendered/oem_b.xlsx
@@ -927,7 +927,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'kind': 'signal', 'signal': 'routine_ready', 'op': '==', 'value': True, 'source_text': 'routine_ready is true'}]</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'kind': 'signal', 'signal': 'speed_kph', 'op': '&lt;', 'value': 5, 'unit': 'km/h', 'source_text': 'speed_kph is below 5 km/h'}]</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'kind': 'signal', 'signal': 'battery_ok', 'op': '==', 'value': True, 'source_text': 'battery ok'}, {'kind': 'signal', 'signal': 'doors_closed', 'op': '==', 'value': True, 'source_text': 'doors closed'}]</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1385,105 +1385,301 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DID 0x2001 may be written only when speed_zero is true.</t>
+          <t>The B-DID-0 data identifier may be written only when ignition_on is true.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Writing DID 0x2001 requires speed_zero to be true.</t>
+          <t>DID 0x2001 may be written only when speed_kph is below 20 km/h.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DID 0x2001 must not be written while speed_zero is false.</t>
+          <t>Writing DID 0x2001 requires speed_kph to be under 20 km/h.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DID 0x2002 may be written only when doors_closed is true.</t>
+          <t>DID 0x2001 must not be written while speed_kph is not below 20 km/h.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Writing DID 0x2002 requires doors_closed to be true.</t>
+          <t>The B-DID-1 data identifier requires speed_kph below 20 km/h.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DID 0x2002 must not be written while doors_closed is false.</t>
+          <t>DID 0x2002 may be written only when battery_v is below 12 V.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DID 0x2003 may be written only when battery_ok is true.</t>
+          <t>Writing DID 0x2002 requires battery_v to be under 12 V.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Writing DID 0x2003 requires battery_ok to be true.</t>
+          <t>DID 0x2002 must not be written while battery_v is not below 12 V.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DID 0x2003 must not be written while battery_ok is false.</t>
+          <t>The B-DID-2 data identifier requires battery_v below 12 V.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DID 0x2004 may be written only when vehicle_stopped is true.</t>
+          <t>DID 0x2003 may be written only when timeout_ms is below 100 ms.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Writing DID 0x2004 requires vehicle_stopped to be true.</t>
+          <t>Writing DID 0x2003 requires timeout_ms to be under 100 ms.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DID 0x2004 must not be written while vehicle_stopped is false.</t>
+          <t>DID 0x2003 must not be written while timeout_ms is not below 100 ms.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DID 0x2005 may be written only when service_brake is true.</t>
+          <t>The B-DID-3 data identifier requires timeout_ms below 100 ms.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Writing DID 0x2005 requires service_brake to be true.</t>
+          <t>DID 0x2004 may be written only when coolant_c is below 105 °C.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Writing DID 0x2004 requires coolant_c to be under 105 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DID 0x2004 must not be written while coolant_c is not below 105 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>The B-DID-4 data identifier requires coolant_c below 105 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DID 0x2005 may be written only when service_brake is true and doors_closed is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DID 0x2005 may be written only when service_brake is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Writing DID 0x2005 requires service_brake to be true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>DID 0x2005 must not be written while service_brake is false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>The B-DID-5 data identifier may be written only when service_brake is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DID 0x2005 may be written only when doors_closed is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Writing DID 0x2005 requires doors_closed to be true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DID 0x2005 must not be written while doors_closed is false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>The B-DID-5 data identifier may be written only when doors_closed is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Routine 0x3000 may be executed only when routine_ready is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Executing Routine 0x3000 requires routine_ready to be true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Routine 0x3000 must not be executed while routine_ready is false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>The B-Routine-0 routine may be executed only when routine_ready is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Routine 0x3001 may be executed only when speed_kph is below 5 km/h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Executing Routine 0x3001 requires speed_kph to be under 5 km/h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Routine 0x3001 must not be executed while speed_kph is not below 5 km/h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>The B-Routine-1 routine requires speed_kph below 5 km/h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Routine 0x3002 may be executed only when battery_ok is true and doors_closed is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Routine 0x3002 may be executed only when battery_ok is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Executing Routine 0x3002 requires battery_ok to be true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Routine 0x3002 must not be executed while battery_ok is false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>The B-Routine-2 routine may be executed only when battery_ok is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Routine 0x3002 may be executed only when doors_closed is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Executing Routine 0x3002 requires doors_closed to be true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Routine 0x3002 must not be executed while doors_closed is false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>The B-Routine-2 routine may be executed only when doors_closed is true.</t>
         </is>
       </c>
     </row>

--- a/data/synthetic/rendered/oem_b.xlsx
+++ b/data/synthetic/rendered/oem_b.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Security" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DIDs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Routines" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Services" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Timing" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Priority" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Appendix" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Metadata" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sessions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Security" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DIDs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Routines" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Services" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Timing" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Priority" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Appendix" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,61 +425,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SYNTH-OEM-B Sessions reference</t>
+          <t>SYNTH-OEM-B Metadata reference</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mode code</t>
+          <t>ecu_name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>oem</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>version</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SYNTH-OEM-B</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>default</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>programming</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>extended</t>
+          <t>OEM-B</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -490,20 +483,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SYNTH-OEM-B Security reference</t>
+          <t>SYNTH-OEM-B Sessions reference</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Access tier</t>
+          <t>Mode code</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -514,11 +507,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>locked</t>
+          <t>default</t>
         </is>
       </c>
     </row>
@@ -528,7 +521,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>level2</t>
+          <t>programming</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>extended</t>
         </is>
       </c>
     </row>
@@ -546,296 +549,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SYNTH-OEM-B DIDs reference</t>
+          <t>SYNTH-OEM-B Security reference</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>Access tier</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Signal name</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Payload octets</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Read modes</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Write modes</t>
+          <t>Label</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>0x2000</t>
-        </is>
+      <c r="A3" t="n">
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B-DID-0</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+          <t>locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>0x2001</t>
-        </is>
-      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B-DID-1</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>0x2002</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>B-DID-2</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>0x2003</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>B-DID-3</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>0x2004</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>B-DID-4</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>0x2005</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>B-DID-5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>0x2006</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>B-DID-6</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>0x2007</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>B-DID-7</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>0x2008</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>B-DID-8</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>0x2009</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>B-DID-9</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>level2</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -847,48 +605,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SYNTH-OEM-B Routines reference</t>
+          <t>SYNTH-OEM-B DIDs reference</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Routine identifier</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Signal name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Payload octets</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Parameter octets</t>
+          <t>Read modes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Allowed modes</t>
+          <t>Write modes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Access tier</t>
+          <t>Encoding</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>Read security</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Write security</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
@@ -897,22 +665,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x3000</t>
+          <t>0x2000</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B-Routine-0</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
+          <t>B-DID-0</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'1': 2, '2': 0}</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -922,34 +688,42 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[{'kind': 'signal', 'signal': 'routine_ready', 'op': '==', 'value': True, 'source_text': 'routine_ready is true'}]</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[{"kind": "signal", "signal": "ignition_on", "op": "==", "value": true, "unit": null, "target": null, "source_text": "ignition on"}]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x3001</t>
+          <t>0x2001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B-Routine-1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
+          <t>B-DID-1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'1': 2, '2': 0}</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -959,34 +733,42 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[{'kind': 'signal', 'signal': 'speed_kph', 'op': '&lt;', 'value': 5, 'unit': 'km/h', 'source_text': 'speed_kph is below 5 km/h'}]</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[{"kind": "signal", "signal": "speed_kph", "op": "&lt;", "value": 20, "unit": "km/h", "target": null, "source_text": "speed_kph is below 20 km/h"}]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x3002</t>
+          <t>0x2002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B-Routine-2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
+          <t>B-DID-2</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'1': 2, '2': 0}</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -996,18 +778,343 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[{'kind': 'signal', 'signal': 'battery_ok', 'op': '==', 'value': True, 'source_text': 'battery ok'}, {'kind': 'signal', 'signal': 'doors_closed', 'op': '==', 'value': True, 'source_text': 'doors closed'}]</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[{"kind": "signal", "signal": "battery_v", "op": "&lt;", "value": 12, "unit": "V", "target": null, "source_text": "battery_v is below 12 V"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0x2003</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B-DID-3</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[{"kind": "signal", "signal": "timeout_ms", "op": "&lt;", "value": 100, "unit": "ms", "target": null, "source_text": "timeout_ms is below 100 ms"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0x2004</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B-DID-4</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[{"kind": "signal", "signal": "coolant_c", "op": "&lt;", "value": 105, "unit": "\u00b0C", "target": null, "source_text": "coolant_c is below 105 \u00b0C"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0x2005</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B-DID-5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[{"kind": "signal", "signal": "service_brake", "op": "==", "value": true, "unit": null, "target": null, "source_text": "service brake"}, {"kind": "signal", "signal": "doors_closed", "op": "==", "value": true, "unit": null, "target": null, "source_text": "doors closed"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0x2006</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B-DID-6</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0x2007</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B-DID-7</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0x2008</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B-DID-8</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x2009</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B-DID-9</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>uint16</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1019,237 +1126,167 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SYNTH-OEM-B Services reference</t>
+          <t>SYNTH-OEM-B Routines reference</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Service code</t>
+          <t>Routine identifier</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Service label</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Session gate</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Security gate</t>
+          <t>Parameter octets</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Subfunctions</t>
+          <t>Allowed modes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>Access tier</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x10</t>
+          <t>0x3000</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DiagnosticSessionControl</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>B-Routine-0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>{'1': 2, '2': 0}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>[{'kind': 'signal', 'signal': 'routine_ready', 'op': '==', 'value': True, 'unit': None, 'target': None, 'source_text': 'routine_ready is true'}]</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x11</t>
+          <t>0x3001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EcuReset</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>B-Routine-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>{'1': 2, '2': 0}</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[{'value': 1, 'name': 'hard'}]</t>
-        </is>
-      </c>
-      <c r="F4" t="b">
-        <v>0</v>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>[{'kind': 'signal', 'signal': 'speed_kph', 'op': '&lt;', 'value': 5, 'unit': 'km/h', 'target': None, 'source_text': 'speed_kph is below 5 km/h'}]</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x22</t>
+          <t>0x3002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ReadDataByIdentifier</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>B-Routine-2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>{'1': 2, '2': 0}</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>0x27</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SecurityAccess</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>0x2E</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>WriteDataByIdentifier</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>0x31</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>RoutineControl</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>0x3E</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TesterPresent</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[{'kind': 'signal', 'signal': 'battery_ok', 'op': '==', 'value': True, 'unit': None, 'target': None, 'source_text': 'battery ok'}, {'kind': 'signal', 'signal': 'doors_closed', 'op': '==', 'value': True, 'unit': None, 'target': None, 'source_text': 'doors closed'}]</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1261,47 +1298,237 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SYNTH-OEM-B Timing reference</t>
+          <t>SYNTH-OEM-B Services reference</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P2 milliseconds</t>
+          <t>Service code</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P2-star milliseconds</t>
+          <t>Service label</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S3 seconds</t>
+          <t>Session gate</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Security gate</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Subfunctions</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SPR</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>75</v>
-      </c>
-      <c r="B3" t="n">
-        <v>7000</v>
-      </c>
-      <c r="C3" t="n">
-        <v>6000</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0x10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DiagnosticSessionControl</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0x11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EcuReset</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[{'value': 1, 'name': 'hard', 'allowed_sessions': [], 'required_security_level': None}]</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0x22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ReadDataByIdentifier</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0x27</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SecurityAccess</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0x2E</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WriteDataByIdentifier</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0x31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RoutineControl</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0x3E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TesterPresent</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1313,33 +1540,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SYNTH-OEM-B Priority reference</t>
+          <t>SYNTH-OEM-B Timing reference</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NRC order</t>
+          <t>P2 milliseconds</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P2-star milliseconds</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>S3 seconds</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>19,18,17,126,127,33,53,36,49,34</t>
-        </is>
+      <c r="A3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1351,6 +1592,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SYNTH-OEM-B Priority reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NRC order</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>19,18,17,126,127,33,53,36,49,34</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/synthetic/rendered/oem_b.xlsx
+++ b/data/synthetic/rendered/oem_b.xlsx
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S3 seconds</t>
+          <t>S3 milliseconds</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19,18,17,126,127,33,53,36,49,34</t>
+          <t>19,18,17,126,127,51,53,36,49,34</t>
         </is>
       </c>
     </row>
